--- a/data/Data bieu do.xlsx
+++ b/data/Data bieu do.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pham.lam\Desktop\supplier-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD8AF96-C77E-4282-AC93-B14EDE94B6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304B3DD-7DCF-4E91-85B1-9AFE1377AC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BD06C460-C8F8-4033-9F48-6DB522E75976}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="46">
   <si>
     <t>Vendor code</t>
   </si>
@@ -144,6 +144,39 @@
   </si>
   <si>
     <t>0.5 (6 months)</t>
+  </si>
+  <si>
+    <t>2021.10.18</t>
+  </si>
+  <si>
+    <t>2024.10.14</t>
+  </si>
+  <si>
+    <t>2020.05.15</t>
+  </si>
+  <si>
+    <t>2021.04.19</t>
+  </si>
+  <si>
+    <t>2024.02.24</t>
+  </si>
+  <si>
+    <t>2026.03.26</t>
+  </si>
+  <si>
+    <t>2020.08.29</t>
+  </si>
+  <si>
+    <t>2022.09.27</t>
+  </si>
+  <si>
+    <t>2023.09.25</t>
+  </si>
+  <si>
+    <t>2024.09.11</t>
+  </si>
+  <si>
+    <t>2024.07.18</t>
   </si>
 </sst>
 </file>
@@ -606,7 +639,7 @@
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="54.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="3" max="3" width="10.6328125" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.90625" customWidth="1"/>
     <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
@@ -647,8 +680,8 @@
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6">
-        <v>2021</v>
+      <c r="C2" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
@@ -676,8 +709,8 @@
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6">
-        <v>2024</v>
+      <c r="C3" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D3" s="8">
         <v>3</v>
@@ -705,8 +738,8 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6">
-        <v>2019</v>
+      <c r="C4" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
@@ -732,8 +765,8 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
-        <v>2021</v>
+      <c r="C5" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -761,8 +794,8 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
-        <v>2024</v>
+      <c r="C6" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="D6" s="8">
         <v>2</v>
@@ -790,8 +823,8 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
-        <v>2026</v>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="D7" s="8">
         <v>3</v>
@@ -819,8 +852,8 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6">
-        <v>2020</v>
+      <c r="C8" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D8" s="8">
         <v>2</v>
@@ -848,8 +881,8 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="6">
-        <v>2022</v>
+      <c r="C9" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
@@ -877,8 +910,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
-        <v>2023</v>
+      <c r="C10" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D10" s="8">
         <v>1</v>
@@ -906,8 +939,8 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
-        <v>2024</v>
+      <c r="C11" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D11" s="8">
         <v>2</v>
@@ -935,8 +968,8 @@
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="6">
-        <v>2024</v>
+      <c r="C12" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D12" s="8">
         <v>2</v>
